--- a/experimental/attention/quant_block_sparse_attention/tests/pytest/cases.xlsx
+++ b/experimental/attention/quant_block_sparse_attention/tests/pytest/cases.xlsx
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
         <v>32</v>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
         <v>32</v>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>32</v>
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
         <v>32</v>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>16</v>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
         <v>32</v>
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
         <v>32</v>
@@ -1347,7 +1347,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
         <v>32</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
         <v>32</v>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
         <v>16</v>
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
         <v>24</v>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
         <v>32</v>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
         <v>32</v>
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
         <v>32</v>
@@ -2040,7 +2040,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>32</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>8</v>
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
         <v>32</v>
@@ -2337,7 +2337,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
         <v>32</v>
@@ -2436,7 +2436,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
         <v>32</v>
@@ -2535,7 +2535,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
         <v>32</v>
@@ -2634,7 +2634,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
         <v>16</v>
@@ -2733,7 +2733,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
         <v>32</v>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
         <v>32</v>
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
         <v>32</v>
@@ -3030,7 +3030,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
         <v>32</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
         <v>24</v>
@@ -3228,7 +3228,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
         <v>32</v>
@@ -3327,7 +3327,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
         <v>32</v>
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
         <v>32</v>
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
         <v>32</v>
@@ -3624,7 +3624,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
         <v>32</v>
@@ -3822,7 +3822,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
         <v>32</v>
@@ -3921,7 +3921,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
         <v>32</v>
@@ -4020,7 +4020,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
         <v>32</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
         <v>16</v>
@@ -4218,7 +4218,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
         <v>32</v>
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
         <v>32</v>
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D41" t="n">
         <v>32</v>
@@ -4515,7 +4515,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
         <v>32</v>
@@ -4614,7 +4614,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
         <v>32</v>
@@ -4713,7 +4713,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
         <v>32</v>
@@ -4812,7 +4812,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
         <v>32</v>
@@ -4911,7 +4911,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
         <v>32</v>
@@ -5010,7 +5010,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D47" t="n">
         <v>32</v>
@@ -5109,7 +5109,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D48" t="n">
         <v>32</v>
@@ -5208,7 +5208,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
         <v>32</v>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
         <v>32</v>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
         <v>32</v>
@@ -5505,7 +5505,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D52" t="n">
         <v>32</v>
@@ -5604,7 +5604,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
         <v>32</v>
@@ -5703,7 +5703,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D54" t="n">
         <v>32</v>
@@ -5802,7 +5802,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
         <v>32</v>
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D56" t="n">
         <v>32</v>
@@ -6000,7 +6000,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D57" t="n">
         <v>32</v>
@@ -6099,7 +6099,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D58" t="n">
         <v>32</v>
@@ -6198,7 +6198,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D59" t="n">
         <v>32</v>
@@ -6297,7 +6297,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D60" t="n">
         <v>32</v>
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D61" t="n">
         <v>32</v>
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
         <v>32</v>
@@ -6594,7 +6594,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D63" t="n">
         <v>32</v>
@@ -6693,7 +6693,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
         <v>32</v>
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D65" t="n">
         <v>32</v>
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D66" t="n">
         <v>32</v>
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
         <v>32</v>
@@ -7089,7 +7089,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D68" t="n">
         <v>32</v>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D69" t="n">
         <v>8</v>
@@ -7287,7 +7287,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D70" t="n">
         <v>24</v>
@@ -7386,7 +7386,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D71" t="n">
         <v>32</v>
